--- a/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
+++ b/InputData/endo-learn/BCSG/BAU CO2 Sequestered Globally.xlsx
@@ -1,32 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\endo-learn\BCSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/endo-learn/BCSG/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_FB935BEBE13A4AC6B23B1B54D269DD6127C6C23E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62801FCB-E22F-4C74-B960-D26C4063DCEC}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22635" windowHeight="13365"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="BCSG" sheetId="3" r:id="rId3"/>
+    <sheet name="SYBCSG" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>BCSG BAU CO2 Sequestered Globally</t>
   </si>
@@ -159,7 +172,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#\ ##0"/>
   </numFmts>
@@ -259,7 +272,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -843,19 +856,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="38.73046875" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -863,69 +876,69 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="12">
         <v>2017</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -933,23 +946,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A15:AN27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="13.1328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:1" ht="23.25" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:40" ht="18" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1065,7 +1078,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>4</v>
       </c>
@@ -1211,7 +1224,7 @@
         <v>645.25886199836145</v>
       </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>5</v>
       </c>
@@ -1357,7 +1370,7 @@
         <v>140.98274447844116</v>
       </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>6</v>
       </c>
@@ -1503,7 +1516,7 @@
         <v>133.61743935810051</v>
       </c>
     </row>
-    <row r="21" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
         <v>7</v>
       </c>
@@ -1649,7 +1662,7 @@
         <v>919.8590458349031</v>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="15.75" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:40" ht="18" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1765,7 +1778,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>4</v>
       </c>
@@ -1913,7 +1926,7 @@
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>5</v>
       </c>
@@ -2061,7 +2074,7 @@
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>6</v>
       </c>
@@ -2209,7 +2222,7 @@
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
         <v>7</v>
       </c>
@@ -2364,17 +2377,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <tabColor theme="3"/>
+    <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AJ2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.3984375" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B1">
         <v>2016</v>
       </c>
@@ -2481,7 +2494,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:36" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>21</v>
       </c>
@@ -2629,4 +2642,228 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DCF22F5-C8D2-431E-BAB2-152DAA4DF42A}">
+  <sheetPr>
+    <tabColor theme="8" tint="-0.249977111117893"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B1">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="11">
+        <f>Data!G21*10^6</f>
+        <v>137220426.52228951</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1C9C742-3ADA-4816-847E-00541B572F2F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6127CA6E-66E6-4FE5-9CF3-59FB9E20CFB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6281FF6B-198D-4BE2-B0CD-E99D89DEC921}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>